--- a/data/trans_dic/P21D_4_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,17</t>
+          <t>0,47; 2,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,61</t>
+          <t>0,32; 1,67</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,77</t>
+          <t>0,47; 1,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,82</t>
+          <t>0,24; 0,89</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,12</t>
+          <t>0,09; 1,23</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,53</t>
+          <t>0,06; 0,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,31</t>
+          <t>0,49; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,78</t>
+          <t>0,33; 0,81</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psicológica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5333</t>
+          <t>0; 5392</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1621; 7300</t>
+          <t>1568; 7225</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1963; 9151</t>
+          <t>1799; 9466</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3538</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4859; 16632</t>
+          <t>4409; 16665</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4908; 16901</t>
+          <t>4891; 18293</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5693</t>
+          <t>0; 6147</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 3306</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>573; 6958</t>
+          <t>573; 7640</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1001; 8767</t>
+          <t>1022; 9949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8146; 20746</t>
+          <t>7837; 21558</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10315; 25292</t>
+          <t>10569; 26187</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_4_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P21D_4_R-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,15</t>
+          <t>0,5; 2,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,67</t>
+          <t>0,36; 1,58</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,39</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,78</t>
+          <t>0,54; 1,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,89</t>
+          <t>0,3; 0,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,23</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,6</t>
+          <t>0,06; 0,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,36</t>
+          <t>0,55; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,81</t>
+          <t>0,37; 0,82</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5039</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5392</t>
+          <t>0; 4701</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1568; 7225</t>
+          <t>1794; 8609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1799; 9466</t>
+          <t>2196; 9730</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>10205</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 3329</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4409; 16665</t>
+          <t>5325; 16628</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4891; 18293</t>
+          <t>5840; 17912</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2423</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6147</t>
+          <t>0; 7616</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3306</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>573; 7640</t>
+          <t>591; 6596</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>17667</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1022; 9949</t>
+          <t>987; 8879</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7837; 21558</t>
+          <t>9255; 22911</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10569; 26187</t>
+          <t>11914; 26560</t>
         </is>
       </c>
     </row>
